--- a/Result/profitability/4903.xlsx
+++ b/Result/profitability/4903.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.09875000000000005</v>
+        <v>0.11125</v>
       </c>
       <c r="N2" t="n">
-        <v>9.8925</v>
+        <v>10.86375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1212500000000001</v>
+        <v>0.13625</v>
       </c>
       <c r="N3" t="n">
-        <v>10.85</v>
+        <v>11.3275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1725</v>
+        <v>0.18125</v>
       </c>
       <c r="N4" t="n">
-        <v>12.14875</v>
+        <v>13.17875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>0.26875</v>
+        <v>0.2325</v>
       </c>
       <c r="N5" t="n">
-        <v>13.80875</v>
+        <v>13.81375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2250000000000001</v>
+        <v>0.10875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.7175</v>
+        <v>12.73</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1125</v>
+        <v>0.07375000000000005</v>
       </c>
       <c r="N7" t="n">
-        <v>13.23125</v>
+        <v>13.425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.08250000000000005</v>
+        <v>0.02250000000000004</v>
       </c>
       <c r="N8" t="n">
-        <v>13.71375</v>
+        <v>14.20375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09500000000000003</v>
+        <v>0.09500000000000004</v>
       </c>
       <c r="N9" t="n">
         <v>15.27125</v>
@@ -1899,7 +1899,7 @@
         <v>0.06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.09875000000000003</v>
+        <v>0.09875000000000005</v>
       </c>
       <c r="N12" t="n">
         <v>16.38</v>
@@ -2026,7 +2026,7 @@
         <v>0.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05125000000000004</v>
+        <v>0.05125000000000005</v>
       </c>
       <c r="N13" t="n">
         <v>16.8475</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>460</v>
+      </c>
+      <c r="D75" t="n">
+        <v>407</v>
+      </c>
+      <c r="E75" t="n">
+        <v>53</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.92%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-33</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.297297297297297</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.919999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5205843293492693</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.611111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.03999999999999915</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.003505696757230448</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
